--- a/PREP REQ v2- TEMPLATE.xlsx
+++ b/PREP REQ v2- TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3163680-2171-DA4E-B2C1-A38889778768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5A2B22-0A0E-6E4A-93C8-82D5CC31B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2960" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,19 +33,19 @@
     <t>Prep</t>
   </si>
   <si>
-    <t>QTY</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
     <t>Pulled by Event Team</t>
   </si>
   <si>
-    <t>FOR</t>
+    <t>Date Needed:</t>
   </si>
   <si>
-    <t>Date Needed:</t>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Qty</t>
   </si>
 </sst>
 </file>
@@ -486,19 +486,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
